--- a/AAII_Financials/Quarterly/PHI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PHI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>PHI</t>
   </si>
@@ -656,136 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
@@ -798,89 +799,92 @@
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>902500</v>
+      </c>
+      <c r="E8" s="3">
         <v>931800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>935900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>921900</v>
       </c>
-      <c r="G8" s="3">
-        <v>962500</v>
-      </c>
       <c r="H8" s="3">
-        <v>965200</v>
+        <v>963500</v>
       </c>
       <c r="I8" s="3">
+        <v>963000</v>
+      </c>
+      <c r="J8" s="3">
         <v>962300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>952200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>913200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>965400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>985500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>924200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>934500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>964300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>932800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>875000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>920400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>894400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>872400</v>
-      </c>
-      <c r="V8" s="3">
-        <v>864800</v>
       </c>
       <c r="W8" s="3">
         <v>864800</v>
       </c>
       <c r="X8" s="3">
+        <v>864800</v>
+      </c>
+      <c r="Y8" s="3">
         <v>868900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>853400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>887400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>823900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>834500</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
@@ -902,97 +906,100 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>135900</v>
+      </c>
+      <c r="E9" s="3">
         <v>285800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>241300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>115000</v>
       </c>
-      <c r="G9" s="3">
-        <v>129700</v>
-      </c>
       <c r="H9" s="3">
-        <v>276700</v>
+        <v>130600</v>
       </c>
       <c r="I9" s="3">
+        <v>409900</v>
+      </c>
+      <c r="J9" s="3">
         <v>267800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>120100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>113800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>390700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>275900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>105200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>103900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>255100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>90700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>86300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>89400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>66200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>72600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>80200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>73300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>77900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>55900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>63700</v>
       </c>
-      <c r="AC9" s="3">
-        <v>0</v>
-      </c>
       <c r="AD9" s="3">
         <v>0</v>
       </c>
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
+      <c r="AF9" s="3">
+        <v>0</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
@@ -1006,97 +1013,100 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>766600</v>
+      </c>
+      <c r="E10" s="3">
         <v>646000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>694500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>806900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>832900</v>
       </c>
-      <c r="H10" s="3">
-        <v>688500</v>
-      </c>
       <c r="I10" s="3">
+        <v>553000</v>
+      </c>
+      <c r="J10" s="3">
         <v>694500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>832100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>799500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>574600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>709600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>819000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>830600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>709200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>832700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>784200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>834100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>805000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>784900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>798600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>792200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>788700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>780100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>809500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>767900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>770800</v>
       </c>
-      <c r="AC10" s="3">
-        <v>0</v>
-      </c>
       <c r="AD10" s="3">
         <v>0</v>
       </c>
       <c r="AE10" s="3">
         <v>0</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
+      <c r="AF10" s="3">
+        <v>0</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
@@ -1110,8 +1120,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1148,8 +1161,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1252,8 +1266,11 @@
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,68 +1373,71 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>113600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17700</v>
       </c>
-      <c r="H14" s="3">
-        <v>300</v>
-      </c>
       <c r="I14" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="J14" s="3">
         <v>96900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-5800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-49200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>20200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-15900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,8 +1456,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1445,8 +1465,8 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>3</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>3</v>
@@ -1460,97 +1480,100 @@
       <c r="AJ14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>232100</v>
+      </c>
+      <c r="E15" s="3">
         <v>235500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>185300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>268300</v>
       </c>
-      <c r="G15" s="3">
-        <v>231200</v>
-      </c>
       <c r="H15" s="3">
+        <v>232500</v>
+      </c>
+      <c r="I15" s="3">
         <v>228300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>227400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>230900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>216300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>207300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>404300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>213600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>221900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>215100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1639700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>412700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1018300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>451600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>265300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>237800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>250300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>233800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>319000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>207400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>206200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>200000</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
       <c r="AD15" s="3">
         <v>0</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>3</v>
@@ -1564,8 +1587,11 @@
       <c r="AJ15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1599,89 +1625,90 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>667600</v>
+      </c>
+      <c r="E17" s="3">
         <v>700900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>639100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>710100</v>
       </c>
-      <c r="G17" s="3">
-        <v>699800</v>
-      </c>
       <c r="H17" s="3">
-        <v>706900</v>
+        <v>700700</v>
       </c>
       <c r="I17" s="3">
+        <v>714300</v>
+      </c>
+      <c r="J17" s="3">
         <v>711500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>688800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>680400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>681800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>966600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>655400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>679900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>704200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1315400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>655800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>974600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>612300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>673800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>630100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>671400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>673300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>706700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>639600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>612100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>627200</v>
       </c>
-      <c r="AC17" s="3">
-        <v>0</v>
-      </c>
       <c r="AD17" s="3">
         <v>0</v>
       </c>
@@ -1703,89 +1730,92 @@
       <c r="AJ17" s="3">
         <v>0</v>
       </c>
+      <c r="AK17" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>234900</v>
+      </c>
+      <c r="E18" s="3">
         <v>231000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>296800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>211700</v>
       </c>
-      <c r="G18" s="3">
-        <v>262700</v>
-      </c>
       <c r="H18" s="3">
-        <v>258300</v>
+        <v>262800</v>
       </c>
       <c r="I18" s="3">
+        <v>248600</v>
+      </c>
+      <c r="J18" s="3">
         <v>250800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>263300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>232800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>283500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>268700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>254600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>260100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-382600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>219200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-54300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>282000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>198600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>234700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>193400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>195600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>146700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>247900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>211800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>207300</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
         <v>0</v>
       </c>
@@ -1807,8 +1837,11 @@
       <c r="AJ18" s="3">
         <v>0</v>
       </c>
+      <c r="AK18" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1845,97 +1878,98 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>39700</v>
       </c>
-      <c r="G20" s="3">
-        <v>34500</v>
-      </c>
       <c r="H20" s="3">
-        <v>-19700</v>
+        <v>41700</v>
       </c>
       <c r="I20" s="3">
+        <v>-73800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-17100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>17500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>24000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-63000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>26300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>23000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>52200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>72800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>278700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-21400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-48700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>14900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
@@ -1949,89 +1983,92 @@
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>412700</v>
+      </c>
+      <c r="E21" s="3">
         <v>487300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>490800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>440400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>453500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>550700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>495300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>476800</v>
+      </c>
+      <c r="L21" s="3">
+        <v>425100</v>
+      </c>
+      <c r="M21" s="3">
+        <v>553700</v>
+      </c>
+      <c r="N21" s="3">
+        <v>396900</v>
+      </c>
+      <c r="O21" s="3">
         <v>459400</v>
       </c>
-      <c r="H21" s="3">
-        <v>506300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>495300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>476800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>425100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>553700</v>
-      </c>
-      <c r="M21" s="3">
-        <v>396900</v>
-      </c>
-      <c r="N21" s="3">
-        <v>459400</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>467800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>471900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>490600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>498600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>962100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>487100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>485400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>423800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>458700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>417600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>461600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>458200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>422300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>402900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,89 +2090,92 @@
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>71000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>79800</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>75100</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
+        <v>153200</v>
+      </c>
+      <c r="J22" s="3">
         <v>77500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>126300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>66200</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
         <v>56600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>57700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>51800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>46500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>47500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>44900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>44300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>45500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>51000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>48000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>43500</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
@@ -2157,97 +2197,100 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E23" s="3">
         <v>185600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>115000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>155200</v>
       </c>
-      <c r="G23" s="3">
-        <v>210500</v>
-      </c>
       <c r="H23" s="3">
-        <v>206100</v>
+        <v>203300</v>
       </c>
       <c r="I23" s="3">
+        <v>197700</v>
+      </c>
+      <c r="J23" s="3">
         <v>96900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>227700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>190200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>234900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>225600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>227000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>225100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-388100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>240100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>176000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>214100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>171700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>138500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>163400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>139500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>97200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>199700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>168000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>159300</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>0</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
@@ -2261,97 +2304,100 @@
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E24" s="3">
         <v>38600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35800</v>
       </c>
-      <c r="G24" s="3">
-        <v>48900</v>
-      </c>
       <c r="H24" s="3">
-        <v>47800</v>
+        <v>47100</v>
       </c>
       <c r="I24" s="3">
+        <v>45700</v>
+      </c>
+      <c r="J24" s="3">
         <v>22400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>54500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>58200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>58000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-92300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>34000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>49400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>30900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>33000</v>
       </c>
       <c r="X24" s="3">
         <v>33000</v>
       </c>
       <c r="Y24" s="3">
+        <v>33000</v>
+      </c>
+      <c r="Z24" s="3">
         <v>13600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>57000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>44700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>45000</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
+      <c r="AF24" s="3">
+        <v>0</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
@@ -2365,8 +2411,11 @@
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2469,89 +2518,92 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E26" s="3">
         <v>147000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>86300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>119400</v>
       </c>
-      <c r="G26" s="3">
-        <v>161600</v>
-      </c>
       <c r="H26" s="3">
-        <v>158300</v>
+        <v>156200</v>
       </c>
       <c r="I26" s="3">
+        <v>152000</v>
+      </c>
+      <c r="J26" s="3">
         <v>74600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>173200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>147600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>176100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>167400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>171100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>167100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-295800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>185100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>142000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>164700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>134300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>107600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>130400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>106500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>83600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>142700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>123300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>114200</v>
       </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
       <c r="AD26" s="3">
         <v>0</v>
       </c>
@@ -2573,89 +2625,92 @@
       <c r="AJ26" s="3">
         <v>0</v>
       </c>
+      <c r="AK26" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E27" s="3">
         <v>146000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>83600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>118800</v>
       </c>
-      <c r="G27" s="3">
-        <v>161500</v>
-      </c>
       <c r="H27" s="3">
-        <v>157300</v>
+        <v>155900</v>
       </c>
       <c r="I27" s="3">
+        <v>151000</v>
+      </c>
+      <c r="J27" s="3">
         <v>72700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>172100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>147000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>174400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>166300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>170400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>165700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-295700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>183400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>139700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>163100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>132500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>106000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>128800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>104900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>81800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>141100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>121500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>112800</v>
       </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
       <c r="AD27" s="3">
         <v>0</v>
       </c>
@@ -2677,8 +2732,11 @@
       <c r="AJ27" s="3">
         <v>0</v>
       </c>
+      <c r="AK27" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2781,8 +2839,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2814,37 +2875,37 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-8500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-400</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2885,8 +2946,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2989,8 +3053,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3093,97 +3160,100 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-54300</v>
+      </c>
+      <c r="E32" s="3">
         <v>20900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-39700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-34500</v>
-      </c>
       <c r="H32" s="3">
-        <v>19700</v>
+        <v>-41700</v>
       </c>
       <c r="I32" s="3">
+        <v>73800</v>
+      </c>
+      <c r="J32" s="3">
         <v>17100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-17500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-24000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>63000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-26300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-23000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-52200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-72800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-278700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>21400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>48700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-14900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
@@ -3197,89 +3267,92 @@
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E33" s="3">
         <v>146200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>83900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>119000</v>
       </c>
-      <c r="G33" s="3">
-        <v>161500</v>
-      </c>
       <c r="H33" s="3">
-        <v>157600</v>
+        <v>156100</v>
       </c>
       <c r="I33" s="3">
+        <v>151300</v>
+      </c>
+      <c r="J33" s="3">
         <v>73000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>172300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>147000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>174900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-22800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>166500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>170600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>166000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-304100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>182300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>138900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>162700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>132500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>106000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>128800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>104900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>81800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>141100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>121500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>112800</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
       <c r="AD33" s="3">
         <v>0</v>
       </c>
@@ -3301,8 +3374,11 @@
       <c r="AJ33" s="3">
         <v>0</v>
       </c>
+      <c r="AK33" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3405,89 +3481,92 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E35" s="3">
         <v>146200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>83900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>119000</v>
       </c>
-      <c r="G35" s="3">
-        <v>161500</v>
-      </c>
       <c r="H35" s="3">
-        <v>157600</v>
+        <v>156100</v>
       </c>
       <c r="I35" s="3">
+        <v>151300</v>
+      </c>
+      <c r="J35" s="3">
         <v>73000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>172300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>147000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>174900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-22800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>166500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>170600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>166000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-304100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>182300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>138900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>162700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>132500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>106000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>128800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>104900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>81800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>141100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>121500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>112800</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
       <c r="AD35" s="3">
         <v>0</v>
       </c>
@@ -3509,103 +3588,106 @@
       <c r="AJ35" s="3">
         <v>0</v>
       </c>
+      <c r="AK35" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3618,8 +3700,11 @@
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3656,8 +3741,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3694,97 +3780,98 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>193500</v>
+      </c>
+      <c r="E41" s="3">
         <v>239600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>201500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>173200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>192100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>240200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>172400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>219600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>204800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>250300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>292000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>379300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>292700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>480400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>295300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>188200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>215100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>213700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>187500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>133600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>175100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>199100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>170100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>198500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>151600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>147900</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
       <c r="AD41" s="3">
         <v>0</v>
       </c>
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
+      <c r="AF41" s="3">
+        <v>0</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
@@ -3798,97 +3885,100 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>800</v>
+        <v>12800</v>
       </c>
       <c r="E42" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F42" s="3">
         <v>6300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>165500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>181000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>317100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>315200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>402700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>352700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>416900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>520800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>697300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>579400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>891500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>708200</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>3</v>
+      <c r="AF42" s="3">
+        <v>0</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>3</v>
@@ -3902,97 +3992,100 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>593300</v>
+      </c>
+      <c r="E43" s="3">
         <v>548200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>552300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>538400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>576900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>570100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>568400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>537100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>500700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>525900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>495900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>472400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>481500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>492600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>497000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>457200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>468000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>465200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>414600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>416100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>410600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>433000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>426000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>513300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>591200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>504100</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
+      <c r="AF43" s="3">
+        <v>0</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>3</v>
@@ -4006,97 +4099,100 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E44" s="3">
         <v>38400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>31300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>37300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>43800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>48000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>56900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>34500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>42100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>60300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>43500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>54100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>76600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>63700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>83600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>71400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>71000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>64700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>86900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>76300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>74800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>73000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>79800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>53200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>54800</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
       <c r="AD44" s="3">
         <v>0</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>3</v>
+      <c r="AF44" s="3">
+        <v>0</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>3</v>
@@ -4110,97 +4206,100 @@
       <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>121000</v>
+        <v>109300</v>
       </c>
       <c r="E45" s="3">
+        <v>114200</v>
+      </c>
+      <c r="F45" s="3">
         <v>112500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>121100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>122400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>117000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>112400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>128500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>154000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>146100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>162600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>302100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>313900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>161600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>431100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>325800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>305400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>303600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>236200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>322300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>340900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>322200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>195300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>208900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>220700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>227700</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
         <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
+      <c r="AF45" s="3">
+        <v>0</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
@@ -4214,97 +4313,100 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1212200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1231200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1178900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1063300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1136600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1185800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1099000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1156500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1122200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1261600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1265800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1478700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1410100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1503600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1452500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1235900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1377100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1368700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1305600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1311600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1419900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1549800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1561600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1579900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1908300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1642700</v>
       </c>
-      <c r="AC46" s="3">
-        <v>0</v>
-      </c>
       <c r="AD46" s="3">
         <v>0</v>
       </c>
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
+      <c r="AF46" s="3">
+        <v>0</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
@@ -4318,97 +4420,100 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>949400</v>
+      </c>
+      <c r="E47" s="3">
         <v>969500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>975200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>986900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1018000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1002700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>987600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1015700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>976400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>967100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>988500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>949500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>992300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1018300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1013100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1022700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1030300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1024000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1020200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1041800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1087500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1053800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1022300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1095600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1127400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1132300</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
       <c r="AD47" s="3">
         <v>0</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>3</v>
+      <c r="AF47" s="3">
+        <v>0</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>3</v>
@@ -4422,97 +4527,100 @@
       <c r="AJ47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6106000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6177300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6398900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6367600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6513200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6250100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6149800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6165700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5865800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5900700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5772900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6101100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6177700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6053300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5762000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5520600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5928100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5892000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5717400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5589800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5456100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5277900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5002000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5073500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5011200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4958900</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
-      </c>
       <c r="AD48" s="3">
         <v>0</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
+      <c r="AF48" s="3">
+        <v>0</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
@@ -4526,97 +4634,100 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1046300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1062000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1094100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1104400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1141600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1125400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1109900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1148000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1100700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1144800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1161300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1137400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1165400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1187800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1152800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1063100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1128500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1121600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1104400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1121600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1141800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1163100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1166800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1284700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1290100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1293400</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
       <c r="AD49" s="3">
         <v>0</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
+      <c r="AF49" s="3">
+        <v>0</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
@@ -4630,8 +4741,11 @@
       <c r="AJ49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4734,8 +4848,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4838,97 +4955,100 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>904200</v>
+      </c>
+      <c r="E52" s="3">
         <v>924800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>932300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1104900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1152400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1154700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1124600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1320100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1406000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1496300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1476100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1267900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1281600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1288400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1767000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2091300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1987000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1974900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1913400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1914000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1789900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1552500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1531900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1326100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1399900</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
+      <c r="AF52" s="3">
+        <v>0</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
@@ -4942,8 +5062,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5046,97 +5169,100 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10380200</v>
+      </c>
+      <c r="E54" s="3">
         <v>10545500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10781700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10806000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11161500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10942300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10731300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11063400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10739800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11069700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11002100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11176700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11295200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11356500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11147500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10933400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11451000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11381200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11061000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10978900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10895200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10597200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10284600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10450500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10663100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10427100</v>
       </c>
-      <c r="AC54" s="3">
-        <v>0</v>
-      </c>
       <c r="AD54" s="3">
         <v>0</v>
       </c>
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
+      <c r="AF54" s="3">
+        <v>0</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
@@ -5150,8 +5276,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5188,8 +5317,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5226,97 +5356,98 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>764400</v>
+      </c>
+      <c r="E57" s="3">
         <v>764800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>851700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>806400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>965400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>924400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1010200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1172400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1418100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1359100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1348200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1420500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1445900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1564000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1878600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1827200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1789400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1761000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1672700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1712400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1674800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1471900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1188700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1211500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1540000</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
+      <c r="AF57" s="3">
+        <v>0</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
@@ -5330,89 +5461,92 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>668500</v>
+      </c>
+      <c r="E58" s="3">
         <v>638900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>425900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>447500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>538900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>484500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>528200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>467600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>314600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>307900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>317100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>714800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>790200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>797600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>763900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>564200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>340700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>338600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>283200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>268200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>210300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>172900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>386000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>557500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>748400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>820600</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
@@ -5434,97 +5568,100 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>290600</v>
+      </c>
+      <c r="E59" s="3">
         <v>454200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>296400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>288100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>295900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>488000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>313500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>336900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>291800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>575500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>416500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>350700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>360500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>611000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1769000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1712800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2023700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2011400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1916400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2032000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1981700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2125400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1955900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2054000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1991400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2143400</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
-      </c>
       <c r="AD59" s="3">
         <v>0</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
+      <c r="AF59" s="3">
+        <v>0</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
@@ -5538,97 +5675,100 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2741800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2965400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2702800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2804400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3086000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3279000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3244900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3451500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3430600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3746800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3550100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3976200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4056200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4595900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4411500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4104300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4164700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4139400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3960700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3972900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3904400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3973100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3813800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3800100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3951200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4504100</v>
       </c>
-      <c r="AC60" s="3">
-        <v>0</v>
-      </c>
       <c r="AD60" s="3">
         <v>0</v>
       </c>
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
+      <c r="AF60" s="3">
+        <v>0</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
@@ -5642,89 +5782,92 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5202700</v>
+      </c>
+      <c r="E61" s="3">
         <v>5252500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5675000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5702300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5622800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5397800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5250500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5298900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5080700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5112700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5140400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4871000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4826300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4473400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4451500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4445400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4681200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4652700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4559900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4530800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4449200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4214500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3950200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4041600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4068100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3417700</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5746,97 +5889,100 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E62" s="3">
         <v>77700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>79600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>84700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>70000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>68300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>67100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>65700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>60900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>65900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>67500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>69300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>75800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>249200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>208900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>308800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>306900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>289300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>373300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>353200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>348800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>383400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>343800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>364000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>344200</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
       <c r="AD62" s="3">
         <v>0</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
+      <c r="AF62" s="3">
+        <v>0</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
@@ -5850,8 +5996,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5954,8 +6103,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6058,8 +6210,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6162,97 +6317,100 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8182700</v>
+      </c>
+      <c r="E66" s="3">
         <v>8448600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8606400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8720600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8938300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8903000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8721400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9048300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8784200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9178300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9009600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9104800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9143100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9331200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9205700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8832200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9231800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9175600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8885000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8953300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8783500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8613400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8223400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8268200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8466100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8348400</v>
       </c>
-      <c r="AC66" s="3">
-        <v>0</v>
-      </c>
       <c r="AD66" s="3">
         <v>0</v>
       </c>
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
+      <c r="AF66" s="3">
+        <v>0</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
@@ -6266,8 +6424,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6304,8 +6465,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6408,8 +6570,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6512,88 +6677,91 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E70" s="3">
         <v>8400</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>8700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>8800</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>9000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>8900</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>8800</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>9100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>8700</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>9100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>9200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>9000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>9200</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>9400</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>9100</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>8700</v>
-      </c>
-      <c r="S70" s="3">
-        <v>9200</v>
       </c>
       <c r="T70" s="3">
         <v>9200</v>
       </c>
       <c r="U70" s="3">
+        <v>9200</v>
+      </c>
+      <c r="V70" s="3">
         <v>9000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>9100</v>
-      </c>
-      <c r="W70" s="3">
-        <v>9200</v>
       </c>
       <c r="X70" s="3">
         <v>9200</v>
       </c>
       <c r="Y70" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Z70" s="3">
         <v>9100</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>9700</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>9800</v>
       </c>
       <c r="AB70" s="3">
         <v>9800</v>
       </c>
       <c r="AC70" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
@@ -6616,8 +6784,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6720,97 +6891,100 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>712200</v>
+      </c>
+      <c r="E72" s="3">
         <v>696600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>735900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>659100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>742000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>572000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>583700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>522900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>521400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>389700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>397500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>411600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>442500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>277200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>335800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>617200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>616700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>613000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>604700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>479400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>542100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>413300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>458100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>402200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>418500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>297000</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
       <c r="AD72" s="3">
         <v>0</v>
       </c>
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
+      <c r="AF72" s="3">
+        <v>0</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
@@ -6824,8 +6998,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6928,8 +7105,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7032,8 +7212,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7136,97 +7319,100 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2167900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2067900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2146400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2056600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2193900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2006900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1978500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1983800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1924000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1860700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1890000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1971900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2049400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1920100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1932800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2092500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2210000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2196500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2167000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2016400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2102400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1974500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2052100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2172600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2187200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2069000</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
-      </c>
       <c r="AD76" s="3">
         <v>0</v>
       </c>
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
+      <c r="AF76" s="3">
+        <v>0</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
@@ -7240,8 +7426,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7344,103 +7533,106 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7453,89 +7645,92 @@
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E81" s="3">
         <v>146200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>83900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>119000</v>
       </c>
-      <c r="G81" s="3">
-        <v>161500</v>
-      </c>
       <c r="H81" s="3">
-        <v>157600</v>
+        <v>156100</v>
       </c>
       <c r="I81" s="3">
+        <v>151300</v>
+      </c>
+      <c r="J81" s="3">
         <v>73000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>172300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>147000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>174900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-22800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>166500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>170600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>166000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-304100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>182300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>138900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>162700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>132500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>106000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>128800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>104900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>81800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>141100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>121500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>112800</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
       <c r="AD81" s="3">
         <v>0</v>
       </c>
@@ -7557,8 +7752,11 @@
       <c r="AJ81" s="3">
         <v>0</v>
       </c>
+      <c r="AK81" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7595,89 +7793,90 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>194600</v>
+      </c>
+      <c r="E83" s="3">
         <v>193800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>51500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>197200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>184700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>175500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>319500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>213600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>221900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>215100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-201300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>205500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>511500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>242700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>820400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>207200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>737700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>226500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>265300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>237800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>250300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>233800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>319000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>207400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>206200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>200000</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
@@ -7693,14 +7892,17 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
+      <c r="AI83" s="3">
+        <v>0</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7803,8 +8005,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7907,8 +8112,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8011,8 +8219,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8115,8 +8326,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8219,89 +8433,92 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>374500</v>
+      </c>
+      <c r="E89" s="3">
         <v>375100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>390200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>498800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>392800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>428600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>234400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>304900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>466600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>423100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>359700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>405100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>294300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>490500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>409300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>266100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>680200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>332900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>389000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>462900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>482500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>317400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>357200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>595300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>324500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>323500</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
         <v>0</v>
       </c>
@@ -8317,14 +8534,17 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>3</v>
+      <c r="AI89" s="3">
+        <v>0</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8361,89 +8581,90 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-184600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-204300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-182900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-309200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-318000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-281900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-337100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-320100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-333900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-209500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-181600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-633900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-395700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16370000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-30133000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-22589000</v>
       </c>
       <c r="T91" s="3">
         <v>-22589000</v>
       </c>
       <c r="U91" s="3">
+        <v>-22589000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-19447000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-29391000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6300</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-8200</v>
       </c>
       <c r="AA91" s="3">
         <v>-8200</v>
       </c>
       <c r="AB91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -8459,14 +8680,17 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>3</v>
+      <c r="AI91" s="3">
+        <v>0</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8569,8 +8793,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8673,89 +8900,92 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-186100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-195000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-193500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-293800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-294600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-276800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-318500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-165400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-363300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-297400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-58800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-92800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-562000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-285900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-118200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-163600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-303200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-418000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-351300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-481000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-661900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-370000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-222500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-317500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-388900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-367800</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
@@ -8771,14 +9001,17 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>3</v>
+      <c r="AI94" s="3">
+        <v>0</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8815,8 +9048,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8859,45 +9093,45 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R96" s="3">
         <v>-100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-275500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-163700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-161600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-157400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>5300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-163600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-161200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8919,8 +9153,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9023,8 +9260,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9127,8 +9367,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9231,89 +9474,92 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-231600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-137800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-165800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-220400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-149000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-85900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>65400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-130100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-141600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-188100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-395100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-220800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>86600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-180800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-187100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-434900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-113900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>117700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>64800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-75600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>28700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-107700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-496000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>353700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>170100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -9329,92 +9575,95 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>3</v>
+      <c r="AI100" s="3">
+        <v>0</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-20900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>24700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-7600</v>
       </c>
       <c r="M101" s="3">
         <v>-7600</v>
       </c>
       <c r="N101" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O101" s="3">
         <v>7700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2700</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -9433,95 +9682,98 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>3</v>
+      <c r="AI101" s="3">
+        <v>0</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E102" s="3">
         <v>44000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>30100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-51800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>65400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-39500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-35800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-37700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-95600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>93400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-179000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>96500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-324700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>270100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>34500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>102800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-91100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-150700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-158700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>117300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-231000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>283500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>125700</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
@@ -9537,10 +9789,13 @@
       <c r="AH102" s="3">
         <v>0</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>3</v>
+      <c r="AI102" s="3">
+        <v>0</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
